--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.84292121934284</v>
+        <v>8.586974698143212</v>
       </c>
       <c r="D2" t="n">
-        <v>53.22001706204406</v>
+        <v>8.648252772582159</v>
       </c>
       <c r="E2" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F2" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.25099998374098</v>
+        <v>2.47828749735791</v>
       </c>
       <c r="D3" t="n">
-        <v>15.51958489334396</v>
+        <v>2.521932545168393</v>
       </c>
       <c r="E3" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F3" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.37383680581395</v>
+        <v>7.698248480944767</v>
       </c>
       <c r="D4" t="n">
-        <v>14.66751097100585</v>
+        <v>2.383470532788451</v>
       </c>
       <c r="E4" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F4" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.48846010637294</v>
+        <v>11.7793747672856</v>
       </c>
       <c r="D5" t="n">
-        <v>36.05709320578389</v>
+        <v>5.859277645939883</v>
       </c>
       <c r="E5" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F5" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.40927613547099</v>
+        <v>9.166507372014037</v>
       </c>
       <c r="D6" t="n">
-        <v>9.341330240343321</v>
+        <v>1.51796616405579</v>
       </c>
       <c r="E6" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F6" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.95102780778306</v>
+        <v>7.954542018764747</v>
       </c>
       <c r="D7" t="n">
-        <v>20.66499134200613</v>
+        <v>3.358061093075996</v>
       </c>
       <c r="E7" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F7" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.87750482331524</v>
+        <v>5.342594533788727</v>
       </c>
       <c r="D8" t="n">
-        <v>26.09937183065498</v>
+        <v>4.241147922481434</v>
       </c>
       <c r="E8" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F8" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.80970878696159</v>
+        <v>7.606577677881259</v>
       </c>
       <c r="D9" t="n">
-        <v>38.02776404640758</v>
+        <v>6.179511657541233</v>
       </c>
       <c r="E9" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F9" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.10803612668635</v>
+        <v>4.242555870586532</v>
       </c>
       <c r="D10" t="n">
-        <v>27.08501600932366</v>
+        <v>4.401315101515094</v>
       </c>
       <c r="E10" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F10" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.11848355166183</v>
+        <v>8.144253577145047</v>
       </c>
       <c r="D11" t="n">
-        <v>47.86312963789883</v>
+        <v>7.77775856615856</v>
       </c>
       <c r="E11" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F11" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.49412444322719</v>
+        <v>6.580295222024418</v>
       </c>
       <c r="D12" t="n">
-        <v>41.69244936819159</v>
+        <v>6.775023022331133</v>
       </c>
       <c r="E12" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F12" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.51049633848825</v>
+        <v>3.332955655004341</v>
       </c>
       <c r="D13" t="n">
-        <v>16.45262606192701</v>
+        <v>2.673551735063139</v>
       </c>
       <c r="E13" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F13" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.50945596443785</v>
+        <v>4.795286594221151</v>
       </c>
       <c r="D14" t="n">
-        <v>30.02041473984048</v>
+        <v>4.878317395224077</v>
       </c>
       <c r="E14" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F14" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.34075433363584</v>
+        <v>7.205372579215823</v>
       </c>
       <c r="D15" t="n">
-        <v>19.02803368014933</v>
+        <v>3.092055473024267</v>
       </c>
       <c r="E15" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F15" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>64.80246284234082</v>
+        <v>10.53040021188038</v>
       </c>
       <c r="D16" t="n">
-        <v>40.28449318532523</v>
+        <v>6.54623014261535</v>
       </c>
       <c r="E16" t="n">
-        <v>15.47900239116777</v>
+        <v>2.515337888564764</v>
       </c>
       <c r="F16" t="n">
-        <v>12.84568516005749</v>
+        <v>2.087423838509342</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
